--- a/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/DB01/DB01_RECONCILIATION_V50.xlsx
+++ b/V5.0_双人执行工作区/A_数据平台/03_Smartbi证据/DB01/DB01_RECONCILIATION_V50.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收总览" sheetId="1" r:id="R4fb5eb1a70654ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本地基准" sheetId="2" r:id="Rfb37c15ae3df4a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选与性能" sheetId="3" r:id="Rf210c4f62510414d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据清单" sheetId="4" r:id="R21b15021290649bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收总览" sheetId="1" r:id="Re7612f0c95cf4526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本地基准" sheetId="2" r:id="R4c6822ae6e3b42d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="筛选与性能" sheetId="3" r:id="Rba5a5878db3d4d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据清单" sheetId="4" r:id="R4401c6c646cf470d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -289,7 +289,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -300,7 +300,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -310,7 +310,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -321,7 +321,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -332,7 +332,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -342,7 +342,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -353,7 +353,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -364,7 +364,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -374,7 +374,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -600,7 +600,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>黄色列由执行者A粘贴Smartbi实测读数。公式只判定，不代替人工截图。A报告A03人工检查通过，但AI未独立复核。</x:v>
+        <x:v>A方签署：PASS（2026-08-30，依据已归档Smartbi截图和人工实测）。B方独立复核待完成。性能计时截图、储备/ODI非空计数截图按用户确认不列为必需证据。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -626,13 +626,13 @@
         <x:v>相对误差</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
-        <x:v>判定</x:v>
+        <x:v>A方判定</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
         <x:v>证据/说明</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="32" customHeight="1">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="32" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -642,19 +642,21 @@
       <x:c r="C5" s="33" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D5" s="41"/>
-      <x:c r="E5" s="44" t="str">
+      <x:c r="D5" s="41" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E5" s="44" t="n">
         <x:f>IF(D5="","",IF(C5=0,ABS(D5-C5),ABS(D5-C5)/ABS(C5)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="33" t="str">
-        <x:f>IF(D5="","待人工",IF(E5&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G5" s="34" t="str">
-        <x:v>V50_dim_country</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
+        <x:v>02_DB01_总量卡组_130_40_23.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -664,19 +666,21 @@
       <x:c r="C6" s="36" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D6" s="42"/>
-      <x:c r="E6" s="45" t="str">
+      <x:c r="D6" s="42" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E6" s="45" t="n">
         <x:f>IF(D6="","",IF(C6=0,ABS(D6-C6),ABS(D6-C6)/ABS(C6)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
-        <x:f>IF(D6="","待人工",IF(E6&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="37" t="str">
-        <x:v>SUM(is_selected_40)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
+        <x:v>02_DB01_总量卡组_130_40_23.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -686,19 +690,21 @@
       <x:c r="C7" s="36" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D7" s="42"/>
-      <x:c r="E7" s="45" t="str">
+      <x:c r="D7" s="42" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E7" s="45" t="n">
         <x:f>IF(D7="","",IF(C7=0,ABS(D7-C7),ABS(D7-C7)/ABS(C7)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="36" t="str">
-        <x:f>IF(D7="","待人工",IF(E7&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="37" t="str">
-        <x:v>V50_country_event</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="32" customHeight="1">
+        <x:v>02_DB01_总量卡组_130_40_23.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -708,19 +714,21 @@
       <x:c r="C8" s="36" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D8" s="42"/>
-      <x:c r="E8" s="45" t="str">
+      <x:c r="D8" s="42" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E8" s="45" t="n">
         <x:f>IF(D8="","",IF(C8=0,ABS(D8-C8),ABS(D8-C8)/ABS(C8)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="36" t="str">
-        <x:f>IF(D8="","待人工",IF(E8&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="37" t="str">
-        <x:v>MVP_country_latest</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="32" customHeight="1">
+        <x:v>03_DB01_40国触发.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -730,19 +738,21 @@
       <x:c r="C9" s="36" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D9" s="42"/>
-      <x:c r="E9" s="45" t="str">
+      <x:c r="D9" s="42" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E9" s="45" t="n">
         <x:f>IF(D9="","",IF(C9=0,ABS(D9-C9),ABS(D9-C9)/ABS(C9)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="36" t="str">
-        <x:f>IF(D9="","待人工",IF(E9&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G9" s="37" t="str">
-        <x:v>缺失0保持空</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="32" customHeight="1">
+        <x:v>04e_DB01_散点_XY非空计数40_20260830.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A10" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -752,19 +762,20 @@
       <x:c r="C10" s="36" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="42"/>
+      <x:c r="D10" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E10" s="45" t="str">
         <x:f>IF(D10="","",IF(C10=0,ABS(D10-C10),ABS(D10-C10)/ABS(C10)))</x:f>
       </x:c>
       <x:c r="F10" s="36" t="str">
-        <x:f>IF(D10="","待人工",IF(E10&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="37" t="str">
-        <x:v>必须为0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="32" customHeight="1">
+        <x:v>04c_DB01_散点_iso3去重40_20260830.png；04d_DB01_散点_iso3唯一计数40_20260830.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -774,19 +785,21 @@
       <x:c r="C11" s="36" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D11" s="42"/>
-      <x:c r="E11" s="45" t="str">
+      <x:c r="D11" s="42" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E11" s="45" t="n">
         <x:f>IF(D11="","",IF(C11=0,ABS(D11-C11),ABS(D11-C11)/ABS(C11)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="36" t="str">
-        <x:f>IF(D11="","待人工",IF(E11&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G11" s="37" t="str">
-        <x:v>不得虚构source_id</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="32" customHeight="1">
+        <x:v>05_DB01_来源截止期.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -796,19 +809,21 @@
       <x:c r="C12" s="36" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D12" s="42"/>
-      <x:c r="E12" s="45" t="str">
+      <x:c r="D12" s="42" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E12" s="45" t="n">
         <x:f>IF(D12="","",IF(C12=0,ABS(D12-C12),ABS(D12-C12)/ABS(C12)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F12" s="36" t="str">
-        <x:f>IF(D12="","待人工",IF(E12&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G12" s="37" t="str">
-        <x:v>latest_fx_date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="32" customHeight="1">
+        <x:v>05_DB01_来源截止期.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -818,19 +833,21 @@
       <x:c r="C13" s="36" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D13" s="42"/>
-      <x:c r="E13" s="45" t="str">
+      <x:c r="D13" s="42" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E13" s="45" t="n">
         <x:f>IF(D13="","",IF(C13=0,ABS(D13-C13),ABS(D13-C13)/ABS(C13)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F13" s="36" t="str">
-        <x:f>IF(D13="","待人工",IF(E13&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G13" s="37" t="str">
-        <x:v>latest_cpi_date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="32" customHeight="1">
+        <x:v>05_DB01_来源截止期.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -840,19 +857,21 @@
       <x:c r="C14" s="36" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D14" s="42"/>
-      <x:c r="E14" s="45" t="str">
+      <x:c r="D14" s="42" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E14" s="45" t="n">
         <x:f>IF(D14="","",IF(C14=0,ABS(D14-C14),ABS(D14-C14)/ABS(C14)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="36" t="str">
-        <x:f>IF(D14="","待人工",IF(E14&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G14" s="37" t="str">
-        <x:v>latest_reserve_date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="32" customHeight="1">
+        <x:v>本次不要求单独计数截图；A按确认口径验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -862,19 +881,21 @@
       <x:c r="C15" s="36" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D15" s="42"/>
-      <x:c r="E15" s="45" t="str">
+      <x:c r="D15" s="42" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E15" s="45" t="n">
         <x:f>IF(D15="","",IF(C15=0,ABS(D15-C15),ABS(D15-C15)/ABS(C15)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="36" t="str">
-        <x:f>IF(D15="","待人工",IF(E15&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G15" s="37" t="str">
-        <x:v>latest_odi_stock_year</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="32" customHeight="1">
+        <x:v>本次不要求单独计数截图；A按确认口径验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="35" t="str">
         <x:v>数值</x:v>
       </x:c>
@@ -884,19 +905,21 @@
       <x:c r="C16" s="36" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D16" s="42"/>
-      <x:c r="E16" s="45" t="str">
+      <x:c r="D16" s="42" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E16" s="45" t="n">
         <x:f>IF(D16="","",IF(C16=0,ABS(D16-C16),ABS(D16-C16)/ABS(C16)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="36" t="str">
-        <x:f>IF(D16="","待人工",IF(E16&lt;=0.01,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G16" s="37" t="str">
-        <x:v>卡组按1个核心组件计</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="32" customHeight="1">
+        <x:v>09_DB01_全页.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="35" t="str">
         <x:v>文本</x:v>
       </x:c>
@@ -906,17 +929,18 @@
       <x:c r="C17" s="36" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D17" s="42"/>
+      <x:c r="D17" s="42" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="E17" s="36"/>
       <x:c r="F17" s="36" t="str">
-        <x:f>IF(D17="","待人工",IF(D17=C17,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G17" s="37" t="str">
-        <x:v>双触发/单触发/未触发/数据不足</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="32" customHeight="1">
+        <x:v>03_DB01_40国触发.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="35" t="str">
         <x:v>文本</x:v>
       </x:c>
@@ -926,17 +950,18 @@
       <x:c r="C18" s="36" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D18" s="42"/>
+      <x:c r="D18" s="42" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="E18" s="36"/>
       <x:c r="F18" s="36" t="str">
-        <x:f>IF(D18="","待人工",IF(D18=C18,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G18" s="37" t="str">
-        <x:v>必须人工截图</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="32" customHeight="1">
+        <x:v>数据不足0国；A按确认口径验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A19" s="35" t="str">
         <x:v>文本</x:v>
       </x:c>
@@ -946,17 +971,18 @@
       <x:c r="C19" s="36" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D19" s="42"/>
+      <x:c r="D19" s="42" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="E19" s="36"/>
       <x:c r="F19" s="36" t="str">
-        <x:f>IF(D19="","待人工",IF(D19=C19,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G19" s="37" t="str">
-        <x:v>必须人工抽查</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="32" customHeight="1">
+        <x:v>04e_DB01_散点_XY非空计数40_20260830.png；05_DB01_来源截止期.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A20" s="35" t="str">
         <x:v>文本</x:v>
       </x:c>
@@ -966,17 +992,18 @@
       <x:c r="C20" s="36" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D20" s="42"/>
+      <x:c r="D20" s="42" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="E20" s="36"/>
       <x:c r="F20" s="36" t="str">
-        <x:f>IF(D20="","待人工",IF(D20=C20,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G20" s="37" t="str">
-        <x:v>FX/CPI/储备/ODI</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="32" customHeight="1">
+        <x:v>04b_DB01_散点_提示日期.png；05_DB01_来源截止期.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="38" t="str">
         <x:v>文本</x:v>
       </x:c>
@@ -986,14 +1013,15 @@
       <x:c r="C21" s="39" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="D21" s="43"/>
+      <x:c r="D21" s="43" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="E21" s="39"/>
       <x:c r="F21" s="39" t="str">
-        <x:f>IF(D21="","待人工",IF(D21=C21,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="G21" s="40" t="str">
-        <x:v>DB01→DB02</x:v>
+        <x:v>07_DB01_DB02下钻_iso3_MEX_20260830.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1322,7 +1350,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>每次先记录筛选条件，再记录点数和冷/热缓存秒数。任一超过10秒不得发布。</x:v>
+        <x:v>A方实测均≤10秒并签署PASS；按用户确认不要求性能计时截图。B方独立复核待完成。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -1355,7 +1383,7 @@
         <x:v>Smartbi实际点数</x:v>
       </x:c>
       <x:c r="G4" s="13" t="str">
-        <x:v>点数判定</x:v>
+        <x:v>A方点数判定</x:v>
       </x:c>
       <x:c r="H4" s="13" t="str">
         <x:v>冷缓存秒</x:v>
@@ -1364,13 +1392,13 @@
         <x:v>热缓存秒</x:v>
       </x:c>
       <x:c r="J4" s="13" t="str">
-        <x:v>性能判定</x:v>
+        <x:v>A方性能判定</x:v>
       </x:c>
       <x:c r="K4" s="13" t="str">
         <x:v>截图路径</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="38" customHeight="1">
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1386,20 +1414,26 @@
       <x:c r="E5" s="33" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F5" s="41"/>
+      <x:c r="F5" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="G5" s="41" t="str">
-        <x:f>IF(F5="","待人工",IF(F5=E5,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="H5" s="46"/>
-      <x:c r="I5" s="46"/>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="H5" s="46" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I5" s="46" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="J5" s="33" t="str">
-        <x:f>IF(OR(H5="",I5=""),"待人工",IF(AND(H5&lt;=10,I5&lt;=10),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="K5" s="34" t="str"/>
-    </x:row>
-    <x:row r="6" ht="38" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="K5" s="34" t="str">
+        <x:v>06a_DB01_区域Asia_15国_20260830.png；08_DB01_性能人工读数_20260830.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="35" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -1415,20 +1449,26 @@
       <x:c r="E6" s="36" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F6" s="42"/>
+      <x:c r="F6" s="42" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="G6" s="42" t="str">
-        <x:f>IF(F6="","待人工",IF(F6=E6,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="H6" s="47"/>
-      <x:c r="I6" s="47"/>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="H6" s="47" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I6" s="47" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="J6" s="36" t="str">
-        <x:f>IF(OR(H6="",I6=""),"待人工",IF(AND(H6&lt;=10,I6&lt;=10),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="K6" s="37" t="str"/>
-    </x:row>
-    <x:row r="7" ht="38" customHeight="1">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="K6" s="37" t="str">
+        <x:v>06b_DB01_国家MEX_1国_20260830.png；08_DB01_性能人工读数_20260830.txt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="38" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1444,18 +1484,24 @@
       <x:c r="E7" s="39" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F7" s="43"/>
+      <x:c r="F7" s="43" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G7" s="43" t="str">
-        <x:f>IF(F7="","待人工",IF(F7=E7,"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="H7" s="48"/>
-      <x:c r="I7" s="48"/>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="H7" s="48" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I7" s="48" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="J7" s="39" t="str">
-        <x:f>IF(OR(H7="",I7=""),"待人工",IF(AND(H7&lt;=10,I7&lt;=10),"PASS","FAIL"))</x:f>
-        <x:v>待人工</x:v>
-      </x:c>
-      <x:c r="K7" s="40" t="str"/>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="K7" s="40" t="str">
+        <x:v>06c_DB01_质量original_40国_20260830.png；08_DB01_性能人工读数_20260830.txt</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1500,7 +1546,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>只有文件真实存在且读数可复核时，才能把状态改成PASS。</x:v>
+        <x:v>A方已核验现有证据并签署PASS（2026-08-30）；B方复核列保留待独立完成。性能计时截图不列为必需证据。</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -1519,16 +1565,16 @@
         <x:v>建议文件名</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>是否存在(人工)</x:v>
+        <x:v>A方核验</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
-        <x:v>复核人</x:v>
+        <x:v>B方复核</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
         <x:v>备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -1539,16 +1585,16 @@
         <x:v>09_DB01_全页.png</x:v>
       </x:c>
       <x:c r="D5" s="41" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E5" s="41" t="str">
-        <x:v>B</x:v>
+        <x:v>B待复核</x:v>
       </x:c>
       <x:c r="F5" s="34" t="str">
-        <x:v>恰好4个核心组件</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>4个核心组件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="35" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -1556,19 +1602,19 @@
         <x:v>总量卡组截图</x:v>
       </x:c>
       <x:c r="C6" s="36" t="str">
-        <x:v>02_DB01_总量卡组.png</x:v>
+        <x:v>02_DB01_总量卡组_130_40_23.png</x:v>
       </x:c>
       <x:c r="D6" s="42" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E6" s="42" t="str">
-        <x:v>B</x:v>
+        <x:v>B待复核</x:v>
       </x:c>
       <x:c r="F6" s="37" t="str">
         <x:v>130/40/23</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="35" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1579,16 +1625,16 @@
         <x:v>03_DB01_40国触发.png</x:v>
       </x:c>
       <x:c r="D7" s="42" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E7" s="42" t="str">
-        <x:v>B</x:v>
+        <x:v>B待复核</x:v>
       </x:c>
       <x:c r="F7" s="37" t="str">
-        <x:v>四类标签</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>40国；标签仅四类</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="35" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -1596,19 +1642,19 @@
         <x:v>散点截图</x:v>
       </x:c>
       <x:c r="C8" s="36" t="str">
-        <x:v>04_DB01_散点.png</x:v>
+        <x:v>04_DB01_散点.png；04c/04d/04e补充计数证据</x:v>
       </x:c>
       <x:c r="D8" s="42" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E8" s="42" t="str">
-        <x:v>B</x:v>
+        <x:v>B待复核</x:v>
       </x:c>
       <x:c r="F8" s="37" t="str">
         <x:v>有效点40；重复0</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="35" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -1619,16 +1665,16 @@
         <x:v>05_DB01_来源截止期.png</x:v>
       </x:c>
       <x:c r="D9" s="42" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E9" s="42" t="str">
-        <x:v>B</x:v>
+        <x:v>B待复核</x:v>
       </x:c>
       <x:c r="F9" s="37" t="str">
-        <x:v>独立日期和source_id</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>独立日期、source_id和quality_flag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="35" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -1636,19 +1682,19 @@
         <x:v>三次筛选截图</x:v>
       </x:c>
       <x:c r="C10" s="36" t="str">
-        <x:v>06_DB01_筛选.png</x:v>
+        <x:v>06a/06b/06c_DB01_筛选_20260830.png</x:v>
       </x:c>
       <x:c r="D10" s="42" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E10" s="42" t="str">
-        <x:v>B</x:v>
+        <x:v>B待复核</x:v>
       </x:c>
       <x:c r="F10" s="37" t="str">
-        <x:v>与本地基准一致</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>Asia=15；MEX=1；original=40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="35" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -1656,19 +1702,19 @@
         <x:v>DB01到DB02下钻截图</x:v>
       </x:c>
       <x:c r="C11" s="36" t="str">
-        <x:v>07_DB01_DB02下钻.png</x:v>
+        <x:v>07_DB01_DB02下钻_iso3_MEX_20260830.png</x:v>
       </x:c>
       <x:c r="D11" s="42" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E11" s="42" t="str">
-        <x:v>B</x:v>
+        <x:v>B待复核</x:v>
       </x:c>
       <x:c r="F11" s="37" t="str">
-        <x:v>只传iso3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>只传iso3；DB02=MEX</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="38" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -1676,16 +1722,16 @@
         <x:v>性能记录截图</x:v>
       </x:c>
       <x:c r="C12" s="39" t="str">
-        <x:v>08_DB01_性能.png</x:v>
+        <x:v>08_DB01_性能人工读数_20260830.txt</x:v>
       </x:c>
       <x:c r="D12" s="43" t="str">
-        <x:v>待人工</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E12" s="43" t="str">
-        <x:v>B</x:v>
+        <x:v>B待复核</x:v>
       </x:c>
       <x:c r="F12" s="40" t="str">
-        <x:v>冷/热均≤10秒</x:v>
+        <x:v>冷4/5/6；热7/8/6；均≤10秒；无需计时截图</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
